--- a/workspace/framework_paper/fp-mapping/gradient_fp_mapping_eval/gradient_fp_mapping_eval_times.xlsx
+++ b/workspace/framework_paper/fp-mapping/gradient_fp_mapping_eval/gradient_fp_mapping_eval_times.xlsx
@@ -448,19 +448,19 @@
         <v>0.5</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0002547108015278354</v>
+        <v>0.0002706433204002678</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0006848791765514761</v>
+        <v>0.0007230607583187521</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0005171765817794949</v>
+        <v>0.0005537949444260448</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0004776549385860563</v>
+        <v>0.000507011620211415</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0004765608377056196</v>
+        <v>0.0004818958998657763</v>
       </c>
     </row>
     <row r="3">
@@ -468,19 +468,19 @@
         <v>0.5210526315789473</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0002654208778403699</v>
+        <v>0.0002721249405294657</v>
       </c>
       <c r="C3" t="n">
-        <v>0.000708569978014566</v>
+        <v>0.0007366125611588359</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005395233602030203</v>
+        <v>0.0005528041208162904</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0004963384213624522</v>
+        <v>0.0005121550196781755</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0004894666979089379</v>
+        <v>0.0004919208399951458</v>
       </c>
     </row>
     <row r="4">
@@ -488,19 +488,19 @@
         <v>0.5421052631578948</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0002933124997070991</v>
+        <v>0.0002956350188469514</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007884158147498966</v>
+        <v>0.0007916101382579654</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0005879009421914816</v>
+        <v>0.0005764466640539467</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0005112367612309754</v>
+        <v>0.0005138658406212926</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0005021691240835935</v>
+        <v>0.0005072516627842561</v>
       </c>
     </row>
     <row r="5">
@@ -508,19 +508,19 @@
         <v>0.5631578947368421</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0003032408587750979</v>
+        <v>0.000285529118264094</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0008251975593157112</v>
+        <v>0.0007735866215080023</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0006250308157177642</v>
+        <v>0.0005793284199899063</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0005920474755112082</v>
+        <v>0.0005395408190088346</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0005841057380894199</v>
+        <v>0.0005301534023601562</v>
       </c>
     </row>
     <row r="6">
@@ -528,19 +528,19 @@
         <v>0.5842105263157895</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0002938133600400761</v>
+        <v>0.000303574979188852</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0007757549383677542</v>
+        <v>0.0008267034444725141</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0005813007964752615</v>
+        <v>0.0006015808024676517</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0005384808202506975</v>
+        <v>0.0005592457810416817</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0005305559205589816</v>
+        <v>0.0005409166554454715</v>
       </c>
     </row>
     <row r="7">
@@ -548,19 +548,19 @@
         <v>0.6052631578947368</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0003037791789392941</v>
+        <v>0.0003164117014966905</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008057850046316162</v>
+        <v>0.0008021334174554795</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0006085391616215929</v>
+        <v>0.0005994892376475036</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0005777857394423336</v>
+        <v>0.0005579225195106119</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0005677225178806111</v>
+        <v>0.0005516099825035781</v>
       </c>
     </row>
     <row r="8">
@@ -568,19 +568,19 @@
         <v>0.6263157894736842</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0003110416186973453</v>
+        <v>0.0003478383779292926</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0008539375208783895</v>
+        <v>0.0009547375200781971</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0006314250233117491</v>
+        <v>0.0006952791032381355</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0005928933178074658</v>
+        <v>0.0006314849248155952</v>
       </c>
       <c r="F8" t="n">
-        <v>0.000584868440637365</v>
+        <v>0.0006183566414983944</v>
       </c>
     </row>
     <row r="9">
@@ -588,19 +588,19 @@
         <v>0.6473684210526316</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0003295141397393309</v>
+        <v>0.0003102508379379287</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0008992558182217181</v>
+        <v>0.0008540100778918713</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0006715382746187971</v>
+        <v>0.0006284916191361845</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0006248541997047141</v>
+        <v>0.0005907924991333857</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0006127783382544294</v>
+        <v>0.0005810908792773261</v>
       </c>
     </row>
     <row r="10">
@@ -608,19 +608,19 @@
         <v>0.6684210526315789</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0003351809404557571</v>
+        <v>0.000370513319503516</v>
       </c>
       <c r="C10" t="n">
-        <v>0.002582219978794455</v>
+        <v>0.00260411998257041</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3331214434915455</v>
+        <v>0.333480817998643</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6186200110416393</v>
+        <v>0.620095950847026</v>
       </c>
       <c r="F10" t="n">
-        <v>1.014543046511244</v>
+        <v>1.014418059435557</v>
       </c>
     </row>
     <row r="11">
@@ -628,19 +628,19 @@
         <v>0.6894736842105263</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0003697449804167263</v>
+        <v>0.0003582307416945696</v>
       </c>
       <c r="C11" t="n">
-        <v>0.001035834897775203</v>
+        <v>0.001022921710973605</v>
       </c>
       <c r="D11" t="n">
-        <v>0.07621571147697978</v>
+        <v>0.07628593258734327</v>
       </c>
       <c r="E11" t="n">
-        <v>0.07596649243729189</v>
+        <v>0.07600520526291803</v>
       </c>
       <c r="F11" t="n">
-        <v>0.07591244346927851</v>
+        <v>0.07602481197100133</v>
       </c>
     </row>
     <row r="12">
@@ -648,19 +648,19 @@
         <v>0.7105263157894737</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0003957741786143743</v>
+        <v>0.0003851909411605448</v>
       </c>
       <c r="C12" t="n">
-        <v>0.001150729263899848</v>
+        <v>0.001106322640553117</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3334245928307064</v>
+        <v>0.3337263537512626</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3293500583979767</v>
+        <v>0.3297062505187933</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3292893816321157</v>
+        <v>0.3297992344637168</v>
       </c>
     </row>
     <row r="13">
@@ -668,19 +668,19 @@
         <v>0.7315789473684211</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0005753399594686926</v>
+        <v>0.0006272783182794228</v>
       </c>
       <c r="C13" t="n">
-        <v>0.005890779903857037</v>
+        <v>0.006008927412331104</v>
       </c>
       <c r="D13" t="n">
-        <v>5.590680973232956</v>
+        <v>5.606919833633001</v>
       </c>
       <c r="E13" t="n">
-        <v>5.272695835604099</v>
+        <v>5.281335559894214</v>
       </c>
       <c r="F13" t="n">
-        <v>5.192700957539492</v>
+        <v>5.200769199181232</v>
       </c>
     </row>
     <row r="14">
@@ -688,19 +688,19 @@
         <v>0.7526315789473684</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0005867282609688118</v>
+        <v>0.0006113349617226049</v>
       </c>
       <c r="C14" t="n">
-        <v>0.008128644395619632</v>
+        <v>0.008110504903597757</v>
       </c>
       <c r="D14" t="n">
-        <v>10.69442039176065</v>
+        <v>10.74744020304643</v>
       </c>
       <c r="E14" t="n">
-        <v>11.3791939570487</v>
+        <v>11.43036620533792</v>
       </c>
       <c r="F14" t="n">
-        <v>12.88664967769233</v>
+        <v>12.93914488444861</v>
       </c>
     </row>
     <row r="15">
@@ -708,19 +708,19 @@
         <v>0.7736842105263158</v>
       </c>
       <c r="B15" t="n">
-        <v>0.000542024963942822</v>
+        <v>0.000675062479567714</v>
       </c>
       <c r="C15" t="n">
-        <v>0.02402872758102603</v>
+        <v>0.02373698031064123</v>
       </c>
       <c r="D15" t="n">
-        <v>8.988795644016937</v>
+        <v>9.002037750476738</v>
       </c>
       <c r="E15" t="n">
-        <v>8.551284578358754</v>
+        <v>8.57668651374639</v>
       </c>
       <c r="F15" t="n">
-        <v>7.935233970298432</v>
+        <v>7.949458296984667</v>
       </c>
     </row>
     <row r="16">
@@ -728,19 +728,19 @@
         <v>0.7947368421052632</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0007279599958565086</v>
+        <v>0.0006566958827897906</v>
       </c>
       <c r="C16" t="n">
-        <v>0.03021040434832685</v>
+        <v>0.03016851843567565</v>
       </c>
       <c r="D16" t="n">
-        <v>22.26239307521493</v>
+        <v>22.15946983422153</v>
       </c>
       <c r="E16" t="n">
-        <v>21.87367306540255</v>
+        <v>21.79464526157361</v>
       </c>
       <c r="F16" t="n">
-        <v>29.43240723781753</v>
+        <v>29.40939088805928</v>
       </c>
     </row>
     <row r="17">
@@ -748,19 +748,19 @@
         <v>0.8157894736842105</v>
       </c>
       <c r="B17" t="n">
-        <v>0.0006243957180413418</v>
+        <v>0.0006428575003519654</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05565071459859609</v>
+        <v>0.05559987323358655</v>
       </c>
       <c r="D17" t="n">
-        <v>13.03006683450309</v>
+        <v>13.0468492466223</v>
       </c>
       <c r="E17" t="n">
-        <v>21.31131780050695</v>
+        <v>21.36191056590644</v>
       </c>
       <c r="F17" t="n">
-        <v>26.27104920568294</v>
+        <v>26.3028516581119</v>
       </c>
     </row>
     <row r="18">
@@ -768,19 +768,19 @@
         <v>0.8368421052631578</v>
       </c>
       <c r="B18" t="n">
-        <v>0.0006060866615734995</v>
+        <v>0.0006691607832908631</v>
       </c>
       <c r="C18" t="n">
-        <v>0.07957092050928623</v>
+        <v>0.08037966136354953</v>
       </c>
       <c r="D18" t="n">
-        <v>27.77437373781402</v>
+        <v>27.82440498228185</v>
       </c>
       <c r="E18" t="n">
-        <v>35.31427736751269</v>
+        <v>35.41501488578157</v>
       </c>
       <c r="F18" t="n">
-        <v>45.24239986153319</v>
+        <v>45.3622178015078</v>
       </c>
     </row>
     <row r="19">
@@ -788,19 +788,19 @@
         <v>0.8578947368421053</v>
       </c>
       <c r="B19" t="n">
-        <v>0.0005484242417151109</v>
+        <v>0.0005198499979451299</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1131761105451733</v>
+        <v>0.1136613118485548</v>
       </c>
       <c r="D19" t="n">
-        <v>41.23085318119847</v>
+        <v>41.26052046778146</v>
       </c>
       <c r="E19" t="n">
-        <v>49.67272421702742</v>
+        <v>49.61963853435591</v>
       </c>
       <c r="F19" t="n">
-        <v>60.65111055524438</v>
+        <v>60.73823252912844</v>
       </c>
     </row>
     <row r="20">
@@ -808,19 +808,19 @@
         <v>0.8789473684210527</v>
       </c>
       <c r="B20" t="n">
-        <v>0.0003852107614511624</v>
+        <v>0.0003761225385824218</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1821751091512852</v>
+        <v>0.1826593241584487</v>
       </c>
       <c r="D20" t="n">
-        <v>52.18055643123458</v>
+        <v>52.37848086397396</v>
       </c>
       <c r="E20" t="n">
-        <v>114.4426181975624</v>
+        <v>114.6272531904152</v>
       </c>
       <c r="F20" t="n">
-        <v>167.7785386735457</v>
+        <v>168.2177386435971</v>
       </c>
     </row>
     <row r="21">
@@ -828,19 +828,19 @@
         <v>0.9</v>
       </c>
       <c r="B21" t="n">
-        <v>0.0003967591826221906</v>
+        <v>0.0003693583782296628</v>
       </c>
       <c r="C21" t="n">
-        <v>0.222932171463035</v>
+        <v>0.2217643076507375</v>
       </c>
       <c r="D21" t="n">
-        <v>182.9892886257055</v>
+        <v>182.1870757550292</v>
       </c>
       <c r="E21" t="n">
-        <v>378.3635992311546</v>
+        <v>376.8641562106833</v>
       </c>
       <c r="F21" t="n">
-        <v>609.7593516251235</v>
+        <v>610.4249738859967</v>
       </c>
     </row>
   </sheetData>
